--- a/macros_alimentos.xlsx
+++ b/macros_alimentos.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mauro\OneDrive\Documentos\Generales\mealprep\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CFB2AE9-DF95-46D5-955B-34CD0FAB8A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED5C9AE2-BC5F-4734-AE85-2D2BCA027CE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="es" sheetId="1" r:id="rId1"/>
+    <sheet name="fr" sheetId="2" r:id="rId2"/>
+    <sheet name="en" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$B$1:$B$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">es!$B$1:$B$72</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="188">
   <si>
     <t>Huevo</t>
   </si>
@@ -47,45 +49,24 @@
     <t>Avena</t>
   </si>
   <si>
-    <t>Chocolate</t>
-  </si>
-  <si>
     <t xml:space="preserve">Banano </t>
   </si>
   <si>
     <t>Almendra</t>
   </si>
   <si>
-    <t>M. Mani</t>
-  </si>
-  <si>
-    <t>Yogurt</t>
-  </si>
-  <si>
     <t>Arroz</t>
   </si>
   <si>
-    <t>Pollo</t>
-  </si>
-  <si>
     <t>Brocoli</t>
   </si>
   <si>
     <t>Cebolla</t>
   </si>
   <si>
-    <t>Pimenton</t>
-  </si>
-  <si>
     <t>Papa</t>
   </si>
   <si>
-    <t>Atun</t>
-  </si>
-  <si>
-    <t>Proteina</t>
-  </si>
-  <si>
     <t>Tomate</t>
   </si>
   <si>
@@ -95,9 +76,6 @@
     <t>Pepino</t>
   </si>
   <si>
-    <t>Aceite Oliva</t>
-  </si>
-  <si>
     <t>name</t>
   </si>
   <si>
@@ -116,21 +94,6 @@
     <t>fiber</t>
   </si>
   <si>
-    <t>Res</t>
-  </si>
-  <si>
-    <t>Cerdo</t>
-  </si>
-  <si>
-    <t>Mix</t>
-  </si>
-  <si>
-    <t>Jamon Pavo</t>
-  </si>
-  <si>
-    <t>Queso Em</t>
-  </si>
-  <si>
     <t>Lentejas</t>
   </si>
   <si>
@@ -140,36 +103,12 @@
     <t>Skyr</t>
   </si>
   <si>
-    <t>Leche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leche Coco </t>
-  </si>
-  <si>
     <t>Parmesano</t>
   </si>
   <si>
-    <t>Charolais</t>
-  </si>
-  <si>
-    <t>Jamon Pollo</t>
-  </si>
-  <si>
-    <t>Res low fat</t>
-  </si>
-  <si>
-    <t>Calabacin</t>
-  </si>
-  <si>
     <t>Tortilla</t>
   </si>
   <si>
-    <t>Sesamo</t>
-  </si>
-  <si>
-    <t>Salsa soya</t>
-  </si>
-  <si>
     <t xml:space="preserve">Zanahoria </t>
   </si>
   <si>
@@ -185,18 +124,9 @@
     <t>Abricot</t>
   </si>
   <si>
-    <t>Peche</t>
-  </si>
-  <si>
-    <t>Leche soya</t>
-  </si>
-  <si>
     <t>Fresa</t>
   </si>
   <si>
-    <t>Frijoles</t>
-  </si>
-  <si>
     <t>Pure</t>
   </si>
   <si>
@@ -209,16 +139,472 @@
     <t>Harina</t>
   </si>
   <si>
-    <t>Pasta</t>
-  </si>
-  <si>
-    <t>Frutos Rojos</t>
-  </si>
-  <si>
     <t>Gnocchi</t>
   </si>
   <si>
     <t>Espinaca</t>
+  </si>
+  <si>
+    <t>Albaricoque</t>
+  </si>
+  <si>
+    <t>Carne 5%</t>
+  </si>
+  <si>
+    <t>Carne 15%</t>
+  </si>
+  <si>
+    <t>Mantequilla de maní</t>
+  </si>
+  <si>
+    <t>Lomo de cerdo</t>
+  </si>
+  <si>
+    <t>Pasta (Fusilli)</t>
+  </si>
+  <si>
+    <t>Chocolate 90%</t>
+  </si>
+  <si>
+    <t>Aceite de oliva</t>
+  </si>
+  <si>
+    <t>Durazno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mix de frutos rojos </t>
+  </si>
+  <si>
+    <t>Jamon de pavo</t>
+  </si>
+  <si>
+    <t>Jamon de pollo</t>
+  </si>
+  <si>
+    <t>Filete de pollo</t>
+  </si>
+  <si>
+    <t>Leche de coco</t>
+  </si>
+  <si>
+    <t>Granos de sésamo</t>
+  </si>
+  <si>
+    <t>Atún</t>
+  </si>
+  <si>
+    <t>Yogur (Fromage blanc 0%)</t>
+  </si>
+  <si>
+    <t>Fríjoles</t>
+  </si>
+  <si>
+    <t>Calabacín</t>
+  </si>
+  <si>
+    <t>Leche entera</t>
+  </si>
+  <si>
+    <t>Champiñones</t>
+  </si>
+  <si>
+    <t>Aguacate</t>
+  </si>
+  <si>
+    <t>Manzana</t>
+  </si>
+  <si>
+    <t>Manzana verde</t>
+  </si>
+  <si>
+    <t>Miel de abejas</t>
+  </si>
+  <si>
+    <t>Miel</t>
+  </si>
+  <si>
+    <t>Naranja</t>
+  </si>
+  <si>
+    <t>Mandarina</t>
+  </si>
+  <si>
+    <t>Pera</t>
+  </si>
+  <si>
+    <t>Uva</t>
+  </si>
+  <si>
+    <t>Melon</t>
+  </si>
+  <si>
+    <t>Mango</t>
+  </si>
+  <si>
+    <t>Kiwi</t>
+  </si>
+  <si>
+    <t>Frambuesa</t>
+  </si>
+  <si>
+    <t>Mora</t>
+  </si>
+  <si>
+    <t>Papaya</t>
+  </si>
+  <si>
+    <t>Pimentón</t>
+  </si>
+  <si>
+    <t>Sandía</t>
+  </si>
+  <si>
+    <t>Melón</t>
+  </si>
+  <si>
+    <t>Brócoli</t>
+  </si>
+  <si>
+    <t>Leche de soya</t>
+  </si>
+  <si>
+    <t>Piña</t>
+  </si>
+  <si>
+    <t>Arándano</t>
+  </si>
+  <si>
+    <t>Maracuyá</t>
+  </si>
+  <si>
+    <t>Laitue</t>
+  </si>
+  <si>
+    <t>Concombre</t>
+  </si>
+  <si>
+    <t>Courgette</t>
+  </si>
+  <si>
+    <t>Champignons</t>
+  </si>
+  <si>
+    <t>Épinards</t>
+  </si>
+  <si>
+    <t>Pastèque</t>
+  </si>
+  <si>
+    <t>Poivron</t>
+  </si>
+  <si>
+    <t>Fraise</t>
+  </si>
+  <si>
+    <t>Purée</t>
+  </si>
+  <si>
+    <t>Pêche</t>
+  </si>
+  <si>
+    <t>Oignon</t>
+  </si>
+  <si>
+    <t>Carotte</t>
+  </si>
+  <si>
+    <t>Lait de soja</t>
+  </si>
+  <si>
+    <t>Mûre</t>
+  </si>
+  <si>
+    <t>Papaye</t>
+  </si>
+  <si>
+    <t>Orange</t>
+  </si>
+  <si>
+    <t>Ananas</t>
+  </si>
+  <si>
+    <t>Yaourt (Fromage blanc 0%)</t>
+  </si>
+  <si>
+    <t>Pomme</t>
+  </si>
+  <si>
+    <t>Framboise</t>
+  </si>
+  <si>
+    <t>Mandarine</t>
+  </si>
+  <si>
+    <t>Poire</t>
+  </si>
+  <si>
+    <t>Myrtille</t>
+  </si>
+  <si>
+    <t>Pomme verte</t>
+  </si>
+  <si>
+    <t>Mangue</t>
+  </si>
+  <si>
+    <t>Mix de fruits rouges</t>
+  </si>
+  <si>
+    <t>Lait entier</t>
+  </si>
+  <si>
+    <t>Raisin</t>
+  </si>
+  <si>
+    <t>Pomme de terre</t>
+  </si>
+  <si>
+    <t>Banane</t>
+  </si>
+  <si>
+    <t>Fruit de la passion</t>
+  </si>
+  <si>
+    <t>Haricots rouges</t>
+  </si>
+  <si>
+    <t>Jambon de dinde</t>
+  </si>
+  <si>
+    <t>Jambon de poulet</t>
+  </si>
+  <si>
+    <t>Filet de poulet</t>
+  </si>
+  <si>
+    <t>Thon</t>
+  </si>
+  <si>
+    <t>Viande 5%</t>
+  </si>
+  <si>
+    <t>Oeuf</t>
+  </si>
+  <si>
+    <t>Avocat</t>
+  </si>
+  <si>
+    <t>Lait de coco</t>
+  </si>
+  <si>
+    <t>Filet de porc</t>
+  </si>
+  <si>
+    <t>Viande 15%</t>
+  </si>
+  <si>
+    <t>Lentilles</t>
+  </si>
+  <si>
+    <t>Farine</t>
+  </si>
+  <si>
+    <t>Riz</t>
+  </si>
+  <si>
+    <t>Pâtes (Fusilli)</t>
+  </si>
+  <si>
+    <t>Flocons d'avoine</t>
+  </si>
+  <si>
+    <t>Biscottes</t>
+  </si>
+  <si>
+    <t>Parmesan</t>
+  </si>
+  <si>
+    <t>Beurre</t>
+  </si>
+  <si>
+    <t>Chocolat 90%</t>
+  </si>
+  <si>
+    <t>Graines de sésame</t>
+  </si>
+  <si>
+    <t>Beurre de cacahuète</t>
+  </si>
+  <si>
+    <t>Amande</t>
+  </si>
+  <si>
+    <t>Huile d'olive</t>
+  </si>
+  <si>
+    <t>Lettuce</t>
+  </si>
+  <si>
+    <t>Cucumber</t>
+  </si>
+  <si>
+    <t>Zucchini</t>
+  </si>
+  <si>
+    <t>Mushrooms</t>
+  </si>
+  <si>
+    <t>Spinach</t>
+  </si>
+  <si>
+    <t>Tomato</t>
+  </si>
+  <si>
+    <t>Watermelon</t>
+  </si>
+  <si>
+    <t>Bell pepper</t>
+  </si>
+  <si>
+    <t>Strawberry</t>
+  </si>
+  <si>
+    <t>Mashed potato</t>
+  </si>
+  <si>
+    <t>Broccoli</t>
+  </si>
+  <si>
+    <t>Peach</t>
+  </si>
+  <si>
+    <t>Onion</t>
+  </si>
+  <si>
+    <t>Carrot</t>
+  </si>
+  <si>
+    <t>Soy milk</t>
+  </si>
+  <si>
+    <t>Blackberry</t>
+  </si>
+  <si>
+    <t>Apricot</t>
+  </si>
+  <si>
+    <t>Pineapple</t>
+  </si>
+  <si>
+    <t>Yogurt (0% fromage blanc)</t>
+  </si>
+  <si>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>Raspberry</t>
+  </si>
+  <si>
+    <t>Tangerine</t>
+  </si>
+  <si>
+    <t>Pear</t>
+  </si>
+  <si>
+    <t>Blueberry</t>
+  </si>
+  <si>
+    <t>Green apple</t>
+  </si>
+  <si>
+    <t>Mixed red berries</t>
+  </si>
+  <si>
+    <t>Whole milk</t>
+  </si>
+  <si>
+    <t>Grapes</t>
+  </si>
+  <si>
+    <t>Potato</t>
+  </si>
+  <si>
+    <t>Banana</t>
+  </si>
+  <si>
+    <t>Passion fruit</t>
+  </si>
+  <si>
+    <t>Red beans</t>
+  </si>
+  <si>
+    <t>Bacon bits</t>
+  </si>
+  <si>
+    <t>Turkey ham</t>
+  </si>
+  <si>
+    <t>Chicken ham</t>
+  </si>
+  <si>
+    <t>Chicken fillet</t>
+  </si>
+  <si>
+    <t>Tuna</t>
+  </si>
+  <si>
+    <t>Beef 5%</t>
+  </si>
+  <si>
+    <t>Egg</t>
+  </si>
+  <si>
+    <t>Avocado</t>
+  </si>
+  <si>
+    <t>Coconut milk</t>
+  </si>
+  <si>
+    <t>Pork tenderloin</t>
+  </si>
+  <si>
+    <t>Beef 15%</t>
+  </si>
+  <si>
+    <t>Honey</t>
+  </si>
+  <si>
+    <t>Lentils</t>
+  </si>
+  <si>
+    <t>Flour</t>
+  </si>
+  <si>
+    <t>Rice</t>
+  </si>
+  <si>
+    <t>Oats</t>
+  </si>
+  <si>
+    <t>Crackers</t>
+  </si>
+  <si>
+    <t>Butter</t>
+  </si>
+  <si>
+    <t>Dark chocolate 90%</t>
+  </si>
+  <si>
+    <t>Sesame seeds</t>
+  </si>
+  <si>
+    <t>Peanut butter</t>
+  </si>
+  <si>
+    <t>Almond</t>
+  </si>
+  <si>
+    <t>Olive oil</t>
   </si>
 </sst>
 </file>
@@ -277,11 +663,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -562,35 +951,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="23.1796875" style="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B2" s="3">
         <v>15</v>
@@ -613,7 +1005,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B3" s="3">
         <v>16</v>
@@ -636,7 +1028,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B4" s="3">
         <v>17</v>
@@ -658,46 +1050,46 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5" s="3">
-        <v>23</v>
+      <c r="A5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="5">
+        <v>22</v>
       </c>
       <c r="C5" s="3">
-        <v>0.39</v>
-      </c>
-      <c r="D5" s="3">
-        <v>3.63</v>
-      </c>
-      <c r="E5" s="3">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="F5" s="3">
-        <v>2.86</v>
-      </c>
-      <c r="G5" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D5" s="5">
+        <v>3.3</v>
+      </c>
+      <c r="E5" s="5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="G5" s="5">
         <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="B6" s="3">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="D6" s="3">
-        <v>5.8</v>
+        <v>3.63</v>
       </c>
       <c r="E6" s="3">
-        <v>1.4</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F6" s="3">
-        <v>1</v>
+        <v>2.86</v>
       </c>
       <c r="G6" s="3">
         <v>100</v>
@@ -706,19 +1098,19 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B7" s="3">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C7" s="3">
         <v>0.3</v>
       </c>
       <c r="D7" s="3">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="E7" s="3">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="F7" s="3">
         <v>1</v>
@@ -729,45 +1121,45 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="3">
-        <v>32</v>
-      </c>
-      <c r="C8" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="D8" s="3">
-        <v>7.68</v>
-      </c>
-      <c r="E8" s="3">
-        <v>2</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0.67</v>
-      </c>
-      <c r="G8" s="3">
+        <v>71</v>
+      </c>
+      <c r="B8" s="6">
+        <v>30</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D8" s="6">
+        <v>7.6</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="G8" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="B9" s="3">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" s="3">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="D9" s="3">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="E9" s="3">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="F9" s="3">
-        <v>3.3</v>
+        <v>1</v>
       </c>
       <c r="G9" s="3">
         <v>100</v>
@@ -775,22 +1167,22 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="B10" s="3">
         <v>32</v>
       </c>
       <c r="C10" s="3">
-        <v>6.3</v>
+        <v>0.3</v>
       </c>
       <c r="D10" s="3">
-        <v>0</v>
+        <v>7.68</v>
       </c>
       <c r="E10" s="3">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F10" s="3">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="G10" s="3">
         <v>100</v>
@@ -798,22 +1190,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B11" s="3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C11" s="3">
-        <v>0.4</v>
+        <v>6.3</v>
       </c>
       <c r="D11" s="3">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="E11" s="3">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="F11" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G11" s="3">
         <v>100</v>
@@ -821,46 +1213,46 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="3">
-        <v>39</v>
-      </c>
-      <c r="C12" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="D12" s="3">
-        <v>9.5399999999999991</v>
-      </c>
-      <c r="E12" s="3">
-        <v>1.93</v>
-      </c>
-      <c r="F12" s="3">
-        <v>0.91</v>
-      </c>
-      <c r="G12" s="3">
+        <v>72</v>
+      </c>
+      <c r="B12" s="6">
+        <v>34</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D12" s="6">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="F12" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="G12" s="6">
         <v>100</v>
       </c>
       <c r="H12" s="1"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="B13" s="3">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C13" s="3">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="D13" s="3">
-        <v>9</v>
+        <v>1.7</v>
       </c>
       <c r="E13" s="3">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="F13" s="3">
-        <v>1.1000000000000001</v>
+        <v>4</v>
       </c>
       <c r="G13" s="3">
         <v>100</v>
@@ -868,22 +1260,22 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B14" s="3">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C14" s="3">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="D14" s="3">
-        <v>9.58</v>
+        <v>9.5399999999999991</v>
       </c>
       <c r="E14" s="3">
-        <v>2.8</v>
+        <v>1.93</v>
       </c>
       <c r="F14" s="3">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="G14" s="3">
         <v>100</v>
@@ -891,22 +1283,22 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="B15" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15" s="3">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
       <c r="D15" s="3">
-        <v>1.4</v>
+        <v>9</v>
       </c>
       <c r="E15" s="3">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="F15" s="3">
-        <v>3.8</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="G15" s="3">
         <v>100</v>
@@ -914,22 +1306,22 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="B16" s="3">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C16" s="3">
-        <v>0.3</v>
+        <v>0.24</v>
       </c>
       <c r="D16" s="3">
-        <v>11</v>
+        <v>9.58</v>
       </c>
       <c r="E16" s="3">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="F16" s="3">
-        <v>1.4</v>
+        <v>0.93</v>
       </c>
       <c r="G16" s="3">
         <v>100</v>
@@ -937,22 +1329,22 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="B17" s="3">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C17" s="3">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="D17" s="3">
-        <v>4.5999999999999996</v>
+        <v>1.4</v>
       </c>
       <c r="E17" s="3">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F17" s="3">
-        <v>8.5</v>
+        <v>3.8</v>
       </c>
       <c r="G17" s="3">
         <v>100</v>
@@ -960,91 +1352,91 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="3">
-        <v>57</v>
-      </c>
-      <c r="C18" s="3">
-        <v>0.4</v>
-      </c>
-      <c r="D18" s="3">
-        <v>3.6</v>
-      </c>
-      <c r="E18" s="3">
-        <v>0</v>
-      </c>
-      <c r="F18" s="3">
-        <v>9.5</v>
-      </c>
-      <c r="G18" s="3">
+        <v>68</v>
+      </c>
+      <c r="B18" s="6">
+        <v>43</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D18" s="6">
+        <v>9.6</v>
+      </c>
+      <c r="E18" s="6">
+        <v>5.3</v>
+      </c>
+      <c r="F18" s="6">
+        <v>1.4</v>
+      </c>
+      <c r="G18" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B19" s="3">
-        <v>61</v>
-      </c>
-      <c r="C19" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="D19" s="3">
-        <v>10.9</v>
-      </c>
-      <c r="E19" s="3">
-        <v>1.3</v>
-      </c>
-      <c r="F19" s="3">
-        <v>0.9</v>
-      </c>
-      <c r="G19" s="3">
+        <v>69</v>
+      </c>
+      <c r="B19" s="6">
+        <v>43</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="D19" s="6">
+        <v>10.8</v>
+      </c>
+      <c r="E19" s="6">
+        <v>1.7</v>
+      </c>
+      <c r="F19" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="G19" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="3">
-        <v>61</v>
-      </c>
-      <c r="C20" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="D20" s="3">
-        <v>6.5</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="G20" s="3">
+        <v>60</v>
+      </c>
+      <c r="B20" s="6">
+        <v>47</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="D20" s="6">
+        <v>11.8</v>
+      </c>
+      <c r="E20" s="6">
+        <v>2.4</v>
+      </c>
+      <c r="F20" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="G20" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="B21" s="3">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="C21" s="3">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="D21" s="3">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E21" s="3">
-        <v>2.2000000000000002</v>
+        <v>2</v>
       </c>
       <c r="F21" s="3">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="G21" s="3">
         <v>100</v>
@@ -1052,137 +1444,137 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B22" s="3">
-        <v>89</v>
-      </c>
-      <c r="C22" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="D22" s="3">
-        <v>23</v>
-      </c>
-      <c r="E22" s="3">
-        <v>2.6</v>
-      </c>
-      <c r="F22" s="3">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="G22" s="3">
+        <v>75</v>
+      </c>
+      <c r="B22" s="6">
+        <v>50</v>
+      </c>
+      <c r="C22" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="D22" s="6">
+        <v>13.1</v>
+      </c>
+      <c r="E22" s="6">
+        <v>1.4</v>
+      </c>
+      <c r="F22" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="G22" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B23" s="3">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="C23" s="3">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="D23" s="3">
-        <v>12</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="E23" s="3">
-        <v>7</v>
+        <v>0.5</v>
       </c>
       <c r="F23" s="3">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="G23" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="3">
-        <v>101</v>
+      <c r="A24" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="5">
+        <v>52</v>
       </c>
       <c r="C24" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="D24" s="3">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E24" s="3">
-        <v>5.6</v>
-      </c>
-      <c r="F24" s="3">
-        <v>17</v>
-      </c>
-      <c r="G24" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D24" s="5">
+        <v>13.8</v>
+      </c>
+      <c r="E24" s="5">
+        <v>2.4</v>
+      </c>
+      <c r="F24" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="G24" s="5">
         <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B25" s="3">
-        <v>102</v>
-      </c>
-      <c r="C25" s="3">
-        <v>1.3</v>
-      </c>
-      <c r="D25" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="E25" s="3">
-        <v>0</v>
-      </c>
-      <c r="F25" s="3">
-        <v>22</v>
-      </c>
-      <c r="G25" s="3">
+        <v>67</v>
+      </c>
+      <c r="B25" s="6">
+        <v>52</v>
+      </c>
+      <c r="C25" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="D25" s="6">
+        <v>11.9</v>
+      </c>
+      <c r="E25" s="6">
+        <v>6.5</v>
+      </c>
+      <c r="F25" s="6">
+        <v>1.2</v>
+      </c>
+      <c r="G25" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="3">
-        <v>106</v>
-      </c>
-      <c r="C26" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="D26" s="3">
-        <v>0.9</v>
-      </c>
-      <c r="E26" s="3">
-        <v>0</v>
-      </c>
-      <c r="F26" s="3">
-        <v>20</v>
-      </c>
-      <c r="G26" s="3">
+        <v>61</v>
+      </c>
+      <c r="B26" s="6">
+        <v>53</v>
+      </c>
+      <c r="C26" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="D26" s="6">
+        <v>13.3</v>
+      </c>
+      <c r="E26" s="6">
+        <v>1.8</v>
+      </c>
+      <c r="F26" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="G26" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B27" s="3">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="C27" s="3">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="E27" s="3">
         <v>0</v>
       </c>
       <c r="F27" s="3">
-        <v>23</v>
+        <v>9.5</v>
       </c>
       <c r="G27" s="3">
         <v>100</v>
@@ -1190,114 +1582,114 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B28" s="3">
-        <v>109</v>
-      </c>
-      <c r="C28" s="3">
-        <v>1</v>
-      </c>
-      <c r="D28" s="3">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3">
-        <v>0</v>
-      </c>
-      <c r="F28" s="3">
-        <v>25</v>
-      </c>
-      <c r="G28" s="3">
+        <v>62</v>
+      </c>
+      <c r="B28" s="6">
+        <v>57</v>
+      </c>
+      <c r="C28" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="D28" s="6">
+        <v>15.2</v>
+      </c>
+      <c r="E28" s="6">
+        <v>3.1</v>
+      </c>
+      <c r="F28" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="G28" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="3">
-        <v>115</v>
-      </c>
-      <c r="C29" s="3">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="D29" s="3">
-        <v>0.6</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>23</v>
-      </c>
-      <c r="G29" s="3">
+        <v>76</v>
+      </c>
+      <c r="B29" s="6">
+        <v>57</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="D29" s="6">
+        <v>14.5</v>
+      </c>
+      <c r="E29" s="6">
+        <v>2.4</v>
+      </c>
+      <c r="F29" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="G29" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="3">
-        <v>125</v>
+      <c r="A30" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" s="5">
+        <v>58</v>
       </c>
       <c r="C30" s="3">
-        <v>5</v>
-      </c>
-      <c r="D30" s="3">
-        <v>0</v>
-      </c>
-      <c r="E30" s="3">
-        <v>0</v>
-      </c>
-      <c r="F30" s="3">
-        <v>20</v>
-      </c>
-      <c r="G30" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="D30" s="5">
+        <v>13.6</v>
+      </c>
+      <c r="E30" s="5">
+        <v>2.8</v>
+      </c>
+      <c r="F30" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="G30" s="5">
         <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B31" s="3">
-        <v>140</v>
-      </c>
-      <c r="C31" s="3">
-        <v>9.83</v>
-      </c>
-      <c r="D31" s="3">
-        <v>0.27</v>
-      </c>
-      <c r="E31" s="3">
-        <v>0</v>
-      </c>
-      <c r="F31" s="3">
-        <v>12.7</v>
-      </c>
-      <c r="G31" s="3">
+        <v>65</v>
+      </c>
+      <c r="B31" s="6">
+        <v>60</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="D31" s="6">
+        <v>15</v>
+      </c>
+      <c r="E31" s="6">
+        <v>1.6</v>
+      </c>
+      <c r="F31" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="G31" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="B32" s="3">
-        <v>163</v>
+        <v>61</v>
       </c>
       <c r="C32" s="3">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="D32" s="3">
-        <v>35</v>
+        <v>10.9</v>
       </c>
       <c r="E32" s="3">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="F32" s="3">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="G32" s="3">
         <v>100</v>
@@ -1305,45 +1697,45 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B33" s="3">
-        <v>182</v>
-      </c>
-      <c r="C33" s="3">
-        <v>18</v>
-      </c>
-      <c r="D33" s="3">
-        <v>2.9</v>
-      </c>
-      <c r="E33" s="3">
-        <v>0</v>
-      </c>
-      <c r="F33" s="3">
-        <v>2</v>
-      </c>
-      <c r="G33" s="3">
+        <v>66</v>
+      </c>
+      <c r="B33" s="6">
+        <v>61</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="D33" s="6">
+        <v>14.7</v>
+      </c>
+      <c r="E33" s="6">
+        <v>3</v>
+      </c>
+      <c r="F33" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G33" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="B34" s="3">
-        <v>184</v>
+        <v>65</v>
       </c>
       <c r="C34" s="3">
-        <v>12</v>
+        <v>3.6</v>
       </c>
       <c r="D34" s="3">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="E34" s="3">
         <v>0</v>
       </c>
       <c r="F34" s="3">
-        <v>19</v>
+        <v>3.3</v>
       </c>
       <c r="G34" s="3">
         <v>100</v>
@@ -1351,45 +1743,45 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B35" s="3">
-        <v>207</v>
-      </c>
-      <c r="C35" s="3">
-        <v>15</v>
-      </c>
-      <c r="D35" s="3">
-        <v>0</v>
-      </c>
-      <c r="E35" s="3">
-        <v>0</v>
-      </c>
-      <c r="F35" s="3">
-        <v>18</v>
-      </c>
-      <c r="G35" s="3">
+        <v>63</v>
+      </c>
+      <c r="B35" s="6">
+        <v>69</v>
+      </c>
+      <c r="C35" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="D35" s="6">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E35" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="F35" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="G35" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="B36" s="3">
-        <v>319</v>
+        <v>77</v>
       </c>
       <c r="C36" s="3">
-        <v>6.3</v>
+        <v>0.1</v>
       </c>
       <c r="D36" s="3">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="E36" s="3">
-        <v>1.9</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F36" s="3">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G36" s="3">
         <v>100</v>
@@ -1397,22 +1789,22 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="B37" s="3">
-        <v>327</v>
+        <v>89</v>
       </c>
       <c r="C37" s="3">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="D37" s="3">
-        <v>44.5</v>
+        <v>23</v>
       </c>
       <c r="E37" s="3">
-        <v>16.100000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="F37" s="3">
-        <v>25.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="G37" s="3">
         <v>100</v>
@@ -1420,45 +1812,45 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B38" s="3">
-        <v>329</v>
-      </c>
-      <c r="C38" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="D38" s="3">
-        <v>68</v>
-      </c>
-      <c r="E38" s="3">
-        <v>4</v>
-      </c>
-      <c r="F38" s="3">
-        <v>10.5</v>
-      </c>
-      <c r="G38" s="3">
+        <v>77</v>
+      </c>
+      <c r="B38" s="6">
+        <v>97</v>
+      </c>
+      <c r="C38" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="D38" s="6">
+        <v>23.4</v>
+      </c>
+      <c r="E38" s="6">
+        <v>10.4</v>
+      </c>
+      <c r="F38" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G38" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39" s="3">
+        <v>101</v>
+      </c>
+      <c r="C39" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="D39" s="3">
+        <v>12</v>
+      </c>
+      <c r="E39" s="3">
         <v>7</v>
       </c>
-      <c r="B39" s="3">
-        <v>352</v>
-      </c>
-      <c r="C39" s="3">
-        <v>1</v>
-      </c>
-      <c r="D39" s="3">
-        <v>76.7</v>
-      </c>
-      <c r="E39" s="3">
-        <v>1.3</v>
-      </c>
       <c r="F39" s="3">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="G39" s="3">
         <v>100</v>
@@ -1466,22 +1858,22 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="B40" s="3">
-        <v>357</v>
+        <v>101</v>
       </c>
       <c r="C40" s="3">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="D40" s="3">
-        <v>70</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E40" s="3">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="F40" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G40" s="3">
         <v>100</v>
@@ -1489,22 +1881,22 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B41" s="3">
-        <v>359</v>
+        <v>102</v>
       </c>
       <c r="C41" s="3">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="D41" s="3">
-        <v>71</v>
+        <v>0.5</v>
       </c>
       <c r="E41" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F41" s="3">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G41" s="3">
         <v>100</v>
@@ -1512,22 +1904,22 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="B42" s="3">
-        <v>372</v>
+        <v>106</v>
       </c>
       <c r="C42" s="3">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="D42" s="3">
-        <v>58.7</v>
+        <v>0.9</v>
       </c>
       <c r="E42" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="G42" s="3">
         <v>100</v>
@@ -1535,22 +1927,22 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="B43" s="3">
-        <v>378</v>
+        <v>107</v>
       </c>
       <c r="C43" s="3">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="D43" s="3">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="E43" s="3">
         <v>0</v>
       </c>
       <c r="F43" s="3">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="G43" s="3">
         <v>100</v>
@@ -1558,22 +1950,22 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B44" s="3">
-        <v>380</v>
+        <v>109</v>
       </c>
       <c r="C44" s="3">
-        <v>8.6</v>
+        <v>1</v>
       </c>
       <c r="D44" s="3">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="E44" s="3">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="F44" s="3">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G44" s="3">
         <v>100</v>
@@ -1581,22 +1973,22 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B45" s="3">
-        <v>380</v>
+        <v>125</v>
       </c>
       <c r="C45" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D45" s="3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
         <v>0</v>
       </c>
       <c r="F45" s="3">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G45" s="3">
         <v>100</v>
@@ -1604,68 +1996,68 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="B46" s="3">
-        <v>398</v>
+        <v>140</v>
       </c>
       <c r="C46" s="3">
-        <v>29</v>
+        <v>9.83</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="E46" s="3">
         <v>0</v>
       </c>
       <c r="F46" s="3">
-        <v>33</v>
+        <v>12.7</v>
       </c>
       <c r="G46" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A47" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" s="3">
-        <v>409</v>
+      <c r="A47" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47" s="5">
+        <v>160</v>
       </c>
       <c r="C47" s="3">
-        <v>33</v>
-      </c>
-      <c r="D47" s="3">
-        <v>4</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>24</v>
-      </c>
-      <c r="G47" s="3">
+        <v>14.7</v>
+      </c>
+      <c r="D47" s="5">
+        <v>8.5</v>
+      </c>
+      <c r="E47" s="5">
+        <v>6.7</v>
+      </c>
+      <c r="F47" s="5">
+        <v>2</v>
+      </c>
+      <c r="G47" s="5">
         <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="B48" s="3">
-        <v>551</v>
+        <v>163</v>
       </c>
       <c r="C48" s="3">
-        <v>60</v>
+        <v>0.4</v>
       </c>
       <c r="D48" s="3">
-        <v>0.7</v>
+        <v>35</v>
       </c>
       <c r="E48" s="3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="F48" s="3">
-        <v>0.6</v>
+        <v>4.3</v>
       </c>
       <c r="G48" s="3">
         <v>100</v>
@@ -1673,22 +2065,22 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" s="3">
+        <v>182</v>
+      </c>
+      <c r="C49" s="3">
+        <v>18</v>
+      </c>
+      <c r="D49" s="3">
+        <v>2.9</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>2</v>
-      </c>
-      <c r="B49" s="3">
-        <v>579</v>
-      </c>
-      <c r="C49" s="3">
-        <v>46.8</v>
-      </c>
-      <c r="D49" s="3">
-        <v>21.4</v>
-      </c>
-      <c r="E49" s="3">
-        <v>14.5</v>
-      </c>
-      <c r="F49" s="3">
-        <v>10.8</v>
       </c>
       <c r="G49" s="3">
         <v>100</v>
@@ -1696,22 +2088,22 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B50" s="3">
-        <v>595</v>
+        <v>184</v>
       </c>
       <c r="C50" s="3">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="D50" s="3">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="E50" s="3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F50" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G50" s="3">
         <v>100</v>
@@ -1719,68 +2111,68 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="B51" s="3">
-        <v>610</v>
+        <v>207</v>
       </c>
       <c r="C51" s="3">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="D51" s="3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E51" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F51" s="3">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G51" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A52" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B52" s="3">
-        <v>621</v>
+      <c r="A52" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="5">
+        <v>304</v>
       </c>
       <c r="C52" s="3">
-        <v>53.3</v>
-      </c>
-      <c r="D52" s="3">
-        <v>4.8</v>
-      </c>
-      <c r="E52" s="3">
-        <v>12.1</v>
-      </c>
-      <c r="F52" s="3">
-        <v>24.5</v>
-      </c>
-      <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="D52" s="5">
+        <v>82.4</v>
+      </c>
+      <c r="E52" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="F52" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="G52" s="5">
         <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B53" s="3">
-        <v>646</v>
+        <v>319</v>
       </c>
       <c r="C53" s="3">
-        <v>58</v>
+        <v>6.3</v>
       </c>
       <c r="D53" s="3">
-        <v>6.4</v>
+        <v>54</v>
       </c>
       <c r="E53" s="3">
-        <v>8.5</v>
+        <v>1.9</v>
       </c>
       <c r="F53" s="3">
-        <v>20.399999999999999</v>
+        <v>11</v>
       </c>
       <c r="G53" s="3">
         <v>100</v>
@@ -1788,34 +2180,3520 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B54" s="3">
+        <v>327</v>
+      </c>
+      <c r="C54" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="D54" s="3">
+        <v>44.5</v>
+      </c>
+      <c r="E54" s="3">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="F54" s="3">
+        <v>25.1</v>
+      </c>
+      <c r="G54" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A55" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B55" s="3">
+        <v>329</v>
+      </c>
+      <c r="C55" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="D55" s="3">
+        <v>68</v>
+      </c>
+      <c r="E55" s="3">
+        <v>4</v>
+      </c>
+      <c r="F55" s="3">
+        <v>10.5</v>
+      </c>
+      <c r="G55" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A56" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B56" s="3">
+        <v>352</v>
+      </c>
+      <c r="C56" s="3">
+        <v>1</v>
+      </c>
+      <c r="D56" s="3">
+        <v>76.7</v>
+      </c>
+      <c r="E56" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="F56" s="3">
+        <v>8.4</v>
+      </c>
+      <c r="G56" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A57" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B57" s="3">
+        <v>357</v>
+      </c>
+      <c r="C57" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="D57" s="3">
+        <v>70</v>
+      </c>
+      <c r="E57" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="F57" s="3">
+        <v>13</v>
+      </c>
+      <c r="G57" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A58" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B58" s="3">
+        <v>359</v>
+      </c>
+      <c r="C58" s="3">
+        <v>2</v>
+      </c>
+      <c r="D58" s="3">
+        <v>71</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3</v>
+      </c>
+      <c r="F58" s="3">
+        <v>13</v>
+      </c>
+      <c r="G58" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A59" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B59" s="3">
+        <v>372</v>
+      </c>
+      <c r="C59" s="3">
+        <v>7</v>
+      </c>
+      <c r="D59" s="3">
+        <v>58.7</v>
+      </c>
+      <c r="E59" s="3">
+        <v>10</v>
+      </c>
+      <c r="F59" s="3">
+        <v>13.5</v>
+      </c>
+      <c r="G59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A60" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B60" s="3">
+        <v>380</v>
+      </c>
+      <c r="C60" s="3">
+        <v>8.6</v>
+      </c>
+      <c r="D60" s="3">
+        <v>63</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="F60" s="3">
+        <v>11</v>
+      </c>
+      <c r="G60" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A61" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B61" s="3">
+        <v>398</v>
+      </c>
+      <c r="C61" s="3">
+        <v>29</v>
+      </c>
+      <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
+        <v>33</v>
+      </c>
+      <c r="G61" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A62" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B62" s="3">
+        <v>409</v>
+      </c>
+      <c r="C62" s="3">
+        <v>33</v>
+      </c>
+      <c r="D62" s="3">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
+        <v>24</v>
+      </c>
+      <c r="G62" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A63" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B63" s="3">
+        <v>551</v>
+      </c>
+      <c r="C63" s="3">
+        <v>60</v>
+      </c>
+      <c r="D63" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="E63" s="3">
+        <v>0</v>
+      </c>
+      <c r="F63" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="G63" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A64" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B64" s="3">
+        <v>579</v>
+      </c>
+      <c r="C64" s="3">
+        <v>46.8</v>
+      </c>
+      <c r="D64" s="3">
+        <v>21.4</v>
+      </c>
+      <c r="E64" s="3">
+        <v>14.5</v>
+      </c>
+      <c r="F64" s="3">
+        <v>10.8</v>
+      </c>
+      <c r="G64" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A65" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B65" s="3">
+        <v>595</v>
+      </c>
+      <c r="C65" s="3">
+        <v>52</v>
+      </c>
+      <c r="D65" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="E65" s="3">
+        <v>12</v>
+      </c>
+      <c r="F65" s="3">
+        <v>23</v>
+      </c>
+      <c r="G65" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A66" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B66" s="3">
+        <v>610</v>
+      </c>
+      <c r="C66" s="3">
+        <v>48</v>
+      </c>
+      <c r="D66" s="3">
+        <v>13</v>
+      </c>
+      <c r="E66" s="3">
+        <v>7</v>
+      </c>
+      <c r="F66" s="3">
+        <v>28</v>
+      </c>
+      <c r="G66" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A67" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B67" s="3">
+        <v>621</v>
+      </c>
+      <c r="C67" s="3">
+        <v>53.3</v>
+      </c>
+      <c r="D67" s="3">
+        <v>4.8</v>
+      </c>
+      <c r="E67" s="3">
+        <v>12.1</v>
+      </c>
+      <c r="F67" s="3">
+        <v>24.5</v>
+      </c>
+      <c r="G67" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A68" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B68" s="3">
         <v>828</v>
       </c>
-      <c r="C54" s="3">
+      <c r="C68" s="3">
         <v>92</v>
       </c>
-      <c r="D54" s="3">
-        <v>0</v>
-      </c>
-      <c r="E54" s="3">
-        <v>0</v>
-      </c>
-      <c r="F54" s="3">
-        <v>0</v>
-      </c>
-      <c r="G54" s="3">
-        <v>100</v>
-      </c>
+      <c r="D68" s="3">
+        <v>0</v>
+      </c>
+      <c r="E68" s="3">
+        <v>0</v>
+      </c>
+      <c r="F68" s="3">
+        <v>0</v>
+      </c>
+      <c r="G68" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A69"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A70"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A71"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A72"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:B54" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G54">
-      <sortCondition ref="B1:B54"/>
-    </sortState>
-  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G68">
+    <sortCondition ref="B2:B68"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{788E28B5-A09C-4076-8A2C-947E58956BCC}">
+  <dimension ref="A1:G68"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="23.6328125" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="3">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D2" s="3">
+        <v>2.9</v>
+      </c>
+      <c r="E2" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="F2" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="G2" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="3">
+        <v>16</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D3" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="G3" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="3">
+        <v>17</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="G4" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" s="3">
+        <v>22</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D5" s="3">
+        <v>3.3</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="G5" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="3">
+        <v>23</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.39</v>
+      </c>
+      <c r="D6" s="3">
+        <v>3.63</v>
+      </c>
+      <c r="E6" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F6" s="3">
+        <v>2.86</v>
+      </c>
+      <c r="G6" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3">
+        <v>27</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D7" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="3">
+        <v>30</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D8" s="3">
+        <v>7.6</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="G8" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="3">
+        <v>31</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D9" s="3">
+        <v>6</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="3">
+        <v>32</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D10" s="3">
+        <v>7.68</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0.67</v>
+      </c>
+      <c r="G10" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" s="3">
+        <v>32</v>
+      </c>
+      <c r="C11" s="3">
+        <v>6.3</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="3">
+        <v>34</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D12" s="3">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="G12" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="3">
+        <v>36</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1.7</v>
+      </c>
+      <c r="E13" s="3">
+        <v>2.9</v>
+      </c>
+      <c r="F13" s="3">
+        <v>4</v>
+      </c>
+      <c r="G13" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="3">
+        <v>39</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="D14" s="3">
+        <v>9.5399999999999991</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1.93</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.91</v>
+      </c>
+      <c r="G14" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" s="3">
+        <v>40</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D15" s="3">
+        <v>9</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1.7</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G15" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" s="3">
+        <v>41</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0.24</v>
+      </c>
+      <c r="D16" s="3">
+        <v>9.58</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.93</v>
+      </c>
+      <c r="G16" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" s="3">
+        <v>41</v>
+      </c>
+      <c r="C17" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="F17" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="G17" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" s="3">
+        <v>43</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D18" s="3">
+        <v>9.6</v>
+      </c>
+      <c r="E18" s="3">
+        <v>5.3</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="G18" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" s="3">
+        <v>43</v>
+      </c>
+      <c r="C19" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D19" s="3">
+        <v>10.8</v>
+      </c>
+      <c r="E19" s="3">
+        <v>1.7</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="G19" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" s="3">
+        <v>47</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D20" s="3">
+        <v>11.8</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="G20" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="3">
+        <v>48</v>
+      </c>
+      <c r="C21" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D21" s="3">
+        <v>11</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="G21" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" s="3">
+        <v>50</v>
+      </c>
+      <c r="C22" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D22" s="3">
+        <v>13.1</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="G22" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="3">
+        <v>52</v>
+      </c>
+      <c r="C23" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D23" s="3">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="F23" s="3">
+        <v>8.5</v>
+      </c>
+      <c r="G23" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" s="3">
+        <v>52</v>
+      </c>
+      <c r="C24" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D24" s="3">
+        <v>13.8</v>
+      </c>
+      <c r="E24" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="G24" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" s="3">
+        <v>52</v>
+      </c>
+      <c r="C25" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="D25" s="3">
+        <v>11.9</v>
+      </c>
+      <c r="E25" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="F25" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="G25" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" s="3">
+        <v>53</v>
+      </c>
+      <c r="C26" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D26" s="3">
+        <v>13.3</v>
+      </c>
+      <c r="E26" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="F26" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="G26" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="3">
+        <v>57</v>
+      </c>
+      <c r="C27" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="D27" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="G27" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B28" s="3">
+        <v>57</v>
+      </c>
+      <c r="C28" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D28" s="3">
+        <v>15.2</v>
+      </c>
+      <c r="E28" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="F28" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="G28" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B29" s="3">
+        <v>57</v>
+      </c>
+      <c r="C29" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D29" s="3">
+        <v>14.5</v>
+      </c>
+      <c r="E29" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="G29" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B30" s="3">
+        <v>58</v>
+      </c>
+      <c r="C30" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="D30" s="3">
+        <v>13.6</v>
+      </c>
+      <c r="E30" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="F30" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="G30" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B31" s="3">
+        <v>60</v>
+      </c>
+      <c r="C31" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="D31" s="3">
+        <v>15</v>
+      </c>
+      <c r="E31" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="F31" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="G31" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B32" s="3">
+        <v>61</v>
+      </c>
+      <c r="C32" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="D32" s="3">
+        <v>10.9</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="G32" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="3">
+        <v>61</v>
+      </c>
+      <c r="C33" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D33" s="3">
+        <v>14.7</v>
+      </c>
+      <c r="E33" s="3">
+        <v>3</v>
+      </c>
+      <c r="F33" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G33" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B34" s="3">
+        <v>65</v>
+      </c>
+      <c r="C34" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="D34" s="3">
+        <v>4.8</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3">
+        <v>3.3</v>
+      </c>
+      <c r="G34" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B35" s="3">
+        <v>69</v>
+      </c>
+      <c r="C35" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D35" s="3">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="F35" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="G35" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" s="3">
+        <v>77</v>
+      </c>
+      <c r="C36" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D36" s="3">
+        <v>17</v>
+      </c>
+      <c r="E36" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F36" s="3">
+        <v>2</v>
+      </c>
+      <c r="G36" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B37" s="3">
+        <v>89</v>
+      </c>
+      <c r="C37" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D37" s="3">
+        <v>23</v>
+      </c>
+      <c r="E37" s="3">
+        <v>2.6</v>
+      </c>
+      <c r="F37" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G37" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B38" s="3">
+        <v>97</v>
+      </c>
+      <c r="C38" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="D38" s="3">
+        <v>23.4</v>
+      </c>
+      <c r="E38" s="3">
+        <v>10.4</v>
+      </c>
+      <c r="F38" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G38" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B39" s="3">
+        <v>101</v>
+      </c>
+      <c r="C39" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="D39" s="3">
+        <v>12</v>
+      </c>
+      <c r="E39" s="3">
+        <v>7</v>
+      </c>
+      <c r="F39" s="3">
+        <v>8</v>
+      </c>
+      <c r="G39" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B40" s="3">
+        <v>101</v>
+      </c>
+      <c r="C40" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="D40" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E40" s="3">
+        <v>5.6</v>
+      </c>
+      <c r="F40" s="3">
+        <v>17</v>
+      </c>
+      <c r="G40" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A41" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B41" s="3">
+        <v>102</v>
+      </c>
+      <c r="C41" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="D41" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3">
+        <v>22</v>
+      </c>
+      <c r="G41" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B42" s="3">
+        <v>106</v>
+      </c>
+      <c r="C42" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="D42" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>20</v>
+      </c>
+      <c r="G42" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B43" s="3">
+        <v>107</v>
+      </c>
+      <c r="C43" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3">
+        <v>23</v>
+      </c>
+      <c r="G43" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A44" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B44" s="3">
+        <v>109</v>
+      </c>
+      <c r="C44" s="3">
+        <v>1</v>
+      </c>
+      <c r="D44" s="3">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3">
+        <v>25</v>
+      </c>
+      <c r="G44" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B45" s="3">
+        <v>125</v>
+      </c>
+      <c r="C45" s="3">
+        <v>5</v>
+      </c>
+      <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
+        <v>20</v>
+      </c>
+      <c r="G45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B46" s="3">
+        <v>140</v>
+      </c>
+      <c r="C46" s="3">
+        <v>9.83</v>
+      </c>
+      <c r="D46" s="3">
+        <v>0.27</v>
+      </c>
+      <c r="E46" s="3">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3">
+        <v>12.7</v>
+      </c>
+      <c r="G46" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B47" s="3">
+        <v>160</v>
+      </c>
+      <c r="C47" s="3">
+        <v>14.7</v>
+      </c>
+      <c r="D47" s="3">
+        <v>8.5</v>
+      </c>
+      <c r="E47" s="3">
+        <v>6.7</v>
+      </c>
+      <c r="F47" s="3">
+        <v>2</v>
+      </c>
+      <c r="G47" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B48" s="3">
+        <v>163</v>
+      </c>
+      <c r="C48" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="D48" s="3">
+        <v>35</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="F48" s="3">
+        <v>4.3</v>
+      </c>
+      <c r="G48" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A49" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B49" s="3">
+        <v>182</v>
+      </c>
+      <c r="C49" s="3">
+        <v>18</v>
+      </c>
+      <c r="D49" s="3">
+        <v>2.9</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
+        <v>2</v>
+      </c>
+      <c r="G49" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A50" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B50" s="3">
+        <v>184</v>
+      </c>
+      <c r="C50" s="3">
+        <v>12</v>
+      </c>
+      <c r="D50" s="3">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3">
+        <v>0</v>
+      </c>
+      <c r="F50" s="3">
+        <v>19</v>
+      </c>
+      <c r="G50" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A51" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B51" s="3">
+        <v>207</v>
+      </c>
+      <c r="C51" s="3">
+        <v>15</v>
+      </c>
+      <c r="D51" s="3">
+        <v>0</v>
+      </c>
+      <c r="E51" s="3">
+        <v>0</v>
+      </c>
+      <c r="F51" s="3">
+        <v>18</v>
+      </c>
+      <c r="G51" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A52" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="3">
+        <v>304</v>
+      </c>
+      <c r="C52" s="3">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3">
+        <v>82.4</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="G52" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A53" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B53" s="3">
+        <v>319</v>
+      </c>
+      <c r="C53" s="3">
+        <v>6.3</v>
+      </c>
+      <c r="D53" s="3">
+        <v>54</v>
+      </c>
+      <c r="E53" s="3">
+        <v>1.9</v>
+      </c>
+      <c r="F53" s="3">
+        <v>11</v>
+      </c>
+      <c r="G53" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A54" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B54" s="3">
+        <v>327</v>
+      </c>
+      <c r="C54" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="D54" s="3">
+        <v>44.5</v>
+      </c>
+      <c r="E54" s="3">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="F54" s="3">
+        <v>25.1</v>
+      </c>
+      <c r="G54" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A55" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B55" s="3">
+        <v>329</v>
+      </c>
+      <c r="C55" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="D55" s="3">
+        <v>68</v>
+      </c>
+      <c r="E55" s="3">
+        <v>4</v>
+      </c>
+      <c r="F55" s="3">
+        <v>10.5</v>
+      </c>
+      <c r="G55" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A56" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B56" s="3">
+        <v>352</v>
+      </c>
+      <c r="C56" s="3">
+        <v>1</v>
+      </c>
+      <c r="D56" s="3">
+        <v>76.7</v>
+      </c>
+      <c r="E56" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="F56" s="3">
+        <v>8.4</v>
+      </c>
+      <c r="G56" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A57" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B57" s="3">
+        <v>357</v>
+      </c>
+      <c r="C57" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="D57" s="3">
+        <v>70</v>
+      </c>
+      <c r="E57" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="F57" s="3">
+        <v>13</v>
+      </c>
+      <c r="G57" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A58" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B58" s="3">
+        <v>359</v>
+      </c>
+      <c r="C58" s="3">
+        <v>2</v>
+      </c>
+      <c r="D58" s="3">
+        <v>71</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3</v>
+      </c>
+      <c r="F58" s="3">
+        <v>13</v>
+      </c>
+      <c r="G58" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A59" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B59" s="3">
+        <v>372</v>
+      </c>
+      <c r="C59" s="3">
+        <v>7</v>
+      </c>
+      <c r="D59" s="3">
+        <v>58.7</v>
+      </c>
+      <c r="E59" s="3">
+        <v>10</v>
+      </c>
+      <c r="F59" s="3">
+        <v>13.5</v>
+      </c>
+      <c r="G59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A60" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B60" s="3">
+        <v>380</v>
+      </c>
+      <c r="C60" s="3">
+        <v>8.6</v>
+      </c>
+      <c r="D60" s="3">
+        <v>63</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="F60" s="3">
+        <v>11</v>
+      </c>
+      <c r="G60" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A61" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B61" s="3">
+        <v>398</v>
+      </c>
+      <c r="C61" s="3">
+        <v>29</v>
+      </c>
+      <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
+        <v>33</v>
+      </c>
+      <c r="G61" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A62" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B62" s="3">
+        <v>409</v>
+      </c>
+      <c r="C62" s="3">
+        <v>33</v>
+      </c>
+      <c r="D62" s="3">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
+        <v>24</v>
+      </c>
+      <c r="G62" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A63" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B63" s="3">
+        <v>551</v>
+      </c>
+      <c r="C63" s="3">
+        <v>60</v>
+      </c>
+      <c r="D63" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="E63" s="3">
+        <v>0</v>
+      </c>
+      <c r="F63" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="G63" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A64" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B64" s="3">
+        <v>579</v>
+      </c>
+      <c r="C64" s="3">
+        <v>46.8</v>
+      </c>
+      <c r="D64" s="3">
+        <v>21.4</v>
+      </c>
+      <c r="E64" s="3">
+        <v>14.5</v>
+      </c>
+      <c r="F64" s="3">
+        <v>10.8</v>
+      </c>
+      <c r="G64" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A65" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B65" s="3">
+        <v>595</v>
+      </c>
+      <c r="C65" s="3">
+        <v>52</v>
+      </c>
+      <c r="D65" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="E65" s="3">
+        <v>12</v>
+      </c>
+      <c r="F65" s="3">
+        <v>23</v>
+      </c>
+      <c r="G65" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A66" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B66" s="3">
+        <v>610</v>
+      </c>
+      <c r="C66" s="3">
+        <v>48</v>
+      </c>
+      <c r="D66" s="3">
+        <v>13</v>
+      </c>
+      <c r="E66" s="3">
+        <v>7</v>
+      </c>
+      <c r="F66" s="3">
+        <v>28</v>
+      </c>
+      <c r="G66" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A67" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B67" s="3">
+        <v>621</v>
+      </c>
+      <c r="C67" s="3">
+        <v>53.3</v>
+      </c>
+      <c r="D67" s="3">
+        <v>4.8</v>
+      </c>
+      <c r="E67" s="3">
+        <v>12.1</v>
+      </c>
+      <c r="F67" s="3">
+        <v>24.5</v>
+      </c>
+      <c r="G67" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A68" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B68" s="3">
+        <v>828</v>
+      </c>
+      <c r="C68" s="3">
+        <v>92</v>
+      </c>
+      <c r="D68" s="3">
+        <v>0</v>
+      </c>
+      <c r="E68" s="3">
+        <v>0</v>
+      </c>
+      <c r="F68" s="3">
+        <v>0</v>
+      </c>
+      <c r="G68" s="3">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8FBD817-E1BD-4944-9E03-1E8664F88DD9}">
+  <dimension ref="A1:G68"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.7265625" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="3">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D2" s="3">
+        <v>2.9</v>
+      </c>
+      <c r="E2" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="F2" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="G2" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B3" s="3">
+        <v>16</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D3" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="G3" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" s="3">
+        <v>17</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="G4" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B5" s="3">
+        <v>22</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D5" s="3">
+        <v>3.3</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="G5" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B6" s="3">
+        <v>23</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0.39</v>
+      </c>
+      <c r="D6" s="3">
+        <v>3.63</v>
+      </c>
+      <c r="E6" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F6" s="3">
+        <v>2.86</v>
+      </c>
+      <c r="G6" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B7" s="3">
+        <v>27</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D7" s="3">
+        <v>5.8</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B8" s="3">
+        <v>30</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D8" s="3">
+        <v>7.6</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="G8" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B9" s="3">
+        <v>31</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D9" s="3">
+        <v>6</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B10" s="3">
+        <v>32</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D10" s="3">
+        <v>7.68</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0.67</v>
+      </c>
+      <c r="G10" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B11" s="3">
+        <v>32</v>
+      </c>
+      <c r="C11" s="3">
+        <v>6.3</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="3">
+        <v>34</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D12" s="3">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="G12" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B13" s="3">
+        <v>36</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1.7</v>
+      </c>
+      <c r="E13" s="3">
+        <v>2.9</v>
+      </c>
+      <c r="F13" s="3">
+        <v>4</v>
+      </c>
+      <c r="G13" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B14" s="3">
+        <v>39</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="D14" s="3">
+        <v>9.5399999999999991</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1.93</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.91</v>
+      </c>
+      <c r="G14" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B15" s="3">
+        <v>40</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D15" s="3">
+        <v>9</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1.7</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G15" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B16" s="3">
+        <v>41</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0.24</v>
+      </c>
+      <c r="D16" s="3">
+        <v>9.58</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.93</v>
+      </c>
+      <c r="G16" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B17" s="3">
+        <v>41</v>
+      </c>
+      <c r="C17" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="F17" s="3">
+        <v>3.8</v>
+      </c>
+      <c r="G17" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B18" s="3">
+        <v>43</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D18" s="3">
+        <v>9.6</v>
+      </c>
+      <c r="E18" s="3">
+        <v>5.3</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="G18" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" s="3">
+        <v>43</v>
+      </c>
+      <c r="C19" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D19" s="3">
+        <v>10.8</v>
+      </c>
+      <c r="E19" s="3">
+        <v>1.7</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="G19" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" s="3">
+        <v>47</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D20" s="3">
+        <v>11.8</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="G20" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B21" s="3">
+        <v>48</v>
+      </c>
+      <c r="C21" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D21" s="3">
+        <v>11</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="G21" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B22" s="3">
+        <v>50</v>
+      </c>
+      <c r="C22" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D22" s="3">
+        <v>13.1</v>
+      </c>
+      <c r="E22" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="G22" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B23" s="3">
+        <v>52</v>
+      </c>
+      <c r="C23" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D23" s="3">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="F23" s="3">
+        <v>8.5</v>
+      </c>
+      <c r="G23" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B24" s="3">
+        <v>52</v>
+      </c>
+      <c r="C24" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D24" s="3">
+        <v>13.8</v>
+      </c>
+      <c r="E24" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="G24" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B25" s="3">
+        <v>52</v>
+      </c>
+      <c r="C25" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="D25" s="3">
+        <v>11.9</v>
+      </c>
+      <c r="E25" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="F25" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="G25" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B26" s="3">
+        <v>53</v>
+      </c>
+      <c r="C26" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D26" s="3">
+        <v>13.3</v>
+      </c>
+      <c r="E26" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="F26" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="G26" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="3">
+        <v>57</v>
+      </c>
+      <c r="C27" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="D27" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="G27" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B28" s="3">
+        <v>57</v>
+      </c>
+      <c r="C28" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D28" s="3">
+        <v>15.2</v>
+      </c>
+      <c r="E28" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="F28" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="G28" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B29" s="3">
+        <v>57</v>
+      </c>
+      <c r="C29" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D29" s="3">
+        <v>14.5</v>
+      </c>
+      <c r="E29" s="3">
+        <v>2.4</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="G29" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B30" s="3">
+        <v>58</v>
+      </c>
+      <c r="C30" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="D30" s="3">
+        <v>13.6</v>
+      </c>
+      <c r="E30" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="F30" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="G30" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B31" s="3">
+        <v>60</v>
+      </c>
+      <c r="C31" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="D31" s="3">
+        <v>15</v>
+      </c>
+      <c r="E31" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="F31" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="G31" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B32" s="3">
+        <v>61</v>
+      </c>
+      <c r="C32" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="D32" s="3">
+        <v>10.9</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="G32" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="3">
+        <v>61</v>
+      </c>
+      <c r="C33" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D33" s="3">
+        <v>14.7</v>
+      </c>
+      <c r="E33" s="3">
+        <v>3</v>
+      </c>
+      <c r="F33" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G33" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B34" s="3">
+        <v>65</v>
+      </c>
+      <c r="C34" s="3">
+        <v>3.6</v>
+      </c>
+      <c r="D34" s="3">
+        <v>4.8</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3">
+        <v>3.3</v>
+      </c>
+      <c r="G34" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B35" s="3">
+        <v>69</v>
+      </c>
+      <c r="C35" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="D35" s="3">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="F35" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="G35" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B36" s="3">
+        <v>77</v>
+      </c>
+      <c r="C36" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D36" s="3">
+        <v>17</v>
+      </c>
+      <c r="E36" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F36" s="3">
+        <v>2</v>
+      </c>
+      <c r="G36" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B37" s="3">
+        <v>89</v>
+      </c>
+      <c r="C37" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="D37" s="3">
+        <v>23</v>
+      </c>
+      <c r="E37" s="3">
+        <v>2.6</v>
+      </c>
+      <c r="F37" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G37" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B38" s="3">
+        <v>97</v>
+      </c>
+      <c r="C38" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="D38" s="3">
+        <v>23.4</v>
+      </c>
+      <c r="E38" s="3">
+        <v>10.4</v>
+      </c>
+      <c r="F38" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G38" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B39" s="3">
+        <v>101</v>
+      </c>
+      <c r="C39" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="D39" s="3">
+        <v>12</v>
+      </c>
+      <c r="E39" s="3">
+        <v>7</v>
+      </c>
+      <c r="F39" s="3">
+        <v>8</v>
+      </c>
+      <c r="G39" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B40" s="3">
+        <v>101</v>
+      </c>
+      <c r="C40" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="D40" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E40" s="3">
+        <v>5.6</v>
+      </c>
+      <c r="F40" s="3">
+        <v>17</v>
+      </c>
+      <c r="G40" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A41" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B41" s="3">
+        <v>102</v>
+      </c>
+      <c r="C41" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="D41" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E41" s="3">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3">
+        <v>22</v>
+      </c>
+      <c r="G41" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B42" s="3">
+        <v>106</v>
+      </c>
+      <c r="C42" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="D42" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>20</v>
+      </c>
+      <c r="G42" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A43" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B43" s="3">
+        <v>107</v>
+      </c>
+      <c r="C43" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3">
+        <v>23</v>
+      </c>
+      <c r="G43" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A44" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B44" s="3">
+        <v>109</v>
+      </c>
+      <c r="C44" s="3">
+        <v>1</v>
+      </c>
+      <c r="D44" s="3">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3">
+        <v>25</v>
+      </c>
+      <c r="G44" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B45" s="3">
+        <v>125</v>
+      </c>
+      <c r="C45" s="3">
+        <v>5</v>
+      </c>
+      <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
+        <v>20</v>
+      </c>
+      <c r="G45" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B46" s="3">
+        <v>140</v>
+      </c>
+      <c r="C46" s="3">
+        <v>9.83</v>
+      </c>
+      <c r="D46" s="3">
+        <v>0.27</v>
+      </c>
+      <c r="E46" s="3">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3">
+        <v>12.7</v>
+      </c>
+      <c r="G46" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B47" s="3">
+        <v>160</v>
+      </c>
+      <c r="C47" s="3">
+        <v>14.7</v>
+      </c>
+      <c r="D47" s="3">
+        <v>8.5</v>
+      </c>
+      <c r="E47" s="3">
+        <v>6.7</v>
+      </c>
+      <c r="F47" s="3">
+        <v>2</v>
+      </c>
+      <c r="G47" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B48" s="3">
+        <v>163</v>
+      </c>
+      <c r="C48" s="3">
+        <v>0.4</v>
+      </c>
+      <c r="D48" s="3">
+        <v>35</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="F48" s="3">
+        <v>4.3</v>
+      </c>
+      <c r="G48" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A49" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B49" s="3">
+        <v>182</v>
+      </c>
+      <c r="C49" s="3">
+        <v>18</v>
+      </c>
+      <c r="D49" s="3">
+        <v>2.9</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
+        <v>2</v>
+      </c>
+      <c r="G49" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A50" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B50" s="3">
+        <v>184</v>
+      </c>
+      <c r="C50" s="3">
+        <v>12</v>
+      </c>
+      <c r="D50" s="3">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3">
+        <v>0</v>
+      </c>
+      <c r="F50" s="3">
+        <v>19</v>
+      </c>
+      <c r="G50" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A51" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B51" s="3">
+        <v>207</v>
+      </c>
+      <c r="C51" s="3">
+        <v>15</v>
+      </c>
+      <c r="D51" s="3">
+        <v>0</v>
+      </c>
+      <c r="E51" s="3">
+        <v>0</v>
+      </c>
+      <c r="F51" s="3">
+        <v>18</v>
+      </c>
+      <c r="G51" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A52" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B52" s="3">
+        <v>304</v>
+      </c>
+      <c r="C52" s="3">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3">
+        <v>82.4</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="F52" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="G52" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A53" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B53" s="3">
+        <v>319</v>
+      </c>
+      <c r="C53" s="3">
+        <v>6.3</v>
+      </c>
+      <c r="D53" s="3">
+        <v>54</v>
+      </c>
+      <c r="E53" s="3">
+        <v>1.9</v>
+      </c>
+      <c r="F53" s="3">
+        <v>11</v>
+      </c>
+      <c r="G53" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A54" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B54" s="3">
+        <v>327</v>
+      </c>
+      <c r="C54" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="D54" s="3">
+        <v>44.5</v>
+      </c>
+      <c r="E54" s="3">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="F54" s="3">
+        <v>25.1</v>
+      </c>
+      <c r="G54" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A55" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B55" s="3">
+        <v>329</v>
+      </c>
+      <c r="C55" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="D55" s="3">
+        <v>68</v>
+      </c>
+      <c r="E55" s="3">
+        <v>4</v>
+      </c>
+      <c r="F55" s="3">
+        <v>10.5</v>
+      </c>
+      <c r="G55" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A56" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B56" s="3">
+        <v>352</v>
+      </c>
+      <c r="C56" s="3">
+        <v>1</v>
+      </c>
+      <c r="D56" s="3">
+        <v>76.7</v>
+      </c>
+      <c r="E56" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="F56" s="3">
+        <v>8.4</v>
+      </c>
+      <c r="G56" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A57" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B57" s="3">
+        <v>357</v>
+      </c>
+      <c r="C57" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="D57" s="3">
+        <v>70</v>
+      </c>
+      <c r="E57" s="3">
+        <v>5.2</v>
+      </c>
+      <c r="F57" s="3">
+        <v>13</v>
+      </c>
+      <c r="G57" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A58" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B58" s="3">
+        <v>359</v>
+      </c>
+      <c r="C58" s="3">
+        <v>2</v>
+      </c>
+      <c r="D58" s="3">
+        <v>71</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3</v>
+      </c>
+      <c r="F58" s="3">
+        <v>13</v>
+      </c>
+      <c r="G58" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A59" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B59" s="3">
+        <v>372</v>
+      </c>
+      <c r="C59" s="3">
+        <v>7</v>
+      </c>
+      <c r="D59" s="3">
+        <v>58.7</v>
+      </c>
+      <c r="E59" s="3">
+        <v>10</v>
+      </c>
+      <c r="F59" s="3">
+        <v>13.5</v>
+      </c>
+      <c r="G59" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A60" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B60" s="3">
+        <v>380</v>
+      </c>
+      <c r="C60" s="3">
+        <v>8.6</v>
+      </c>
+      <c r="D60" s="3">
+        <v>63</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3.1</v>
+      </c>
+      <c r="F60" s="3">
+        <v>11</v>
+      </c>
+      <c r="G60" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A61" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B61" s="3">
+        <v>398</v>
+      </c>
+      <c r="C61" s="3">
+        <v>29</v>
+      </c>
+      <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
+        <v>33</v>
+      </c>
+      <c r="G61" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A62" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B62" s="3">
+        <v>409</v>
+      </c>
+      <c r="C62" s="3">
+        <v>33</v>
+      </c>
+      <c r="D62" s="3">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
+        <v>24</v>
+      </c>
+      <c r="G62" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A63" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B63" s="3">
+        <v>551</v>
+      </c>
+      <c r="C63" s="3">
+        <v>60</v>
+      </c>
+      <c r="D63" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="E63" s="3">
+        <v>0</v>
+      </c>
+      <c r="F63" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="G63" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A64" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B64" s="3">
+        <v>579</v>
+      </c>
+      <c r="C64" s="3">
+        <v>46.8</v>
+      </c>
+      <c r="D64" s="3">
+        <v>21.4</v>
+      </c>
+      <c r="E64" s="3">
+        <v>14.5</v>
+      </c>
+      <c r="F64" s="3">
+        <v>10.8</v>
+      </c>
+      <c r="G64" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A65" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B65" s="3">
+        <v>595</v>
+      </c>
+      <c r="C65" s="3">
+        <v>52</v>
+      </c>
+      <c r="D65" s="3">
+        <v>3.2</v>
+      </c>
+      <c r="E65" s="3">
+        <v>12</v>
+      </c>
+      <c r="F65" s="3">
+        <v>23</v>
+      </c>
+      <c r="G65" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A66" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B66" s="3">
+        <v>610</v>
+      </c>
+      <c r="C66" s="3">
+        <v>48</v>
+      </c>
+      <c r="D66" s="3">
+        <v>13</v>
+      </c>
+      <c r="E66" s="3">
+        <v>7</v>
+      </c>
+      <c r="F66" s="3">
+        <v>28</v>
+      </c>
+      <c r="G66" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A67" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B67" s="3">
+        <v>621</v>
+      </c>
+      <c r="C67" s="3">
+        <v>53.3</v>
+      </c>
+      <c r="D67" s="3">
+        <v>4.8</v>
+      </c>
+      <c r="E67" s="3">
+        <v>12.1</v>
+      </c>
+      <c r="F67" s="3">
+        <v>24.5</v>
+      </c>
+      <c r="G67" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A68" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B68" s="3">
+        <v>828</v>
+      </c>
+      <c r="C68" s="3">
+        <v>92</v>
+      </c>
+      <c r="D68" s="3">
+        <v>0</v>
+      </c>
+      <c r="E68" s="3">
+        <v>0</v>
+      </c>
+      <c r="F68" s="3">
+        <v>0</v>
+      </c>
+      <c r="G68" s="3">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/macros_alimentos.xlsx
+++ b/macros_alimentos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mauro\OneDrive\Documentos\Generales\mealprep\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED5C9AE2-BC5F-4734-AE85-2D2BCA027CE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE6F7419-812B-42FD-8EE0-AE586709A2EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="es" sheetId="1" r:id="rId1"/>
@@ -52,9 +52,6 @@
     <t xml:space="preserve">Banano </t>
   </si>
   <si>
-    <t>Almendra</t>
-  </si>
-  <si>
     <t>Arroz</t>
   </si>
   <si>
@@ -127,9 +124,6 @@
     <t>Fresa</t>
   </si>
   <si>
-    <t>Pure</t>
-  </si>
-  <si>
     <t>Panko</t>
   </si>
   <si>
@@ -605,6 +599,12 @@
   </si>
   <si>
     <t>Olive oil</t>
+  </si>
+  <si>
+    <t>Puré</t>
+  </si>
+  <si>
+    <t>Almendras</t>
   </si>
 </sst>
 </file>
@@ -663,14 +663,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -959,30 +956,30 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="G1" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="3">
         <v>15</v>
@@ -1005,7 +1002,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="3">
         <v>16</v>
@@ -1028,7 +1025,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B4" s="3">
         <v>17</v>
@@ -1050,31 +1047,31 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B5" s="5">
+      <c r="A5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="3">
         <v>22</v>
       </c>
       <c r="C5" s="3">
         <v>0.3</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="3">
         <v>3.3</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="3">
         <v>1</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="3">
         <v>3.1</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B6" s="3">
         <v>23</v>
@@ -1098,7 +1095,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" s="3">
         <v>27</v>
@@ -1121,30 +1118,30 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B8" s="6">
+        <v>69</v>
+      </c>
+      <c r="B8" s="3">
         <v>30</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="3">
         <v>0.2</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="3">
         <v>7.6</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="3">
         <v>0.4</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="3">
         <v>0.6</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B9" s="3">
         <v>31</v>
@@ -1167,7 +1164,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B10" s="3">
         <v>32</v>
@@ -1190,7 +1187,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>28</v>
+        <v>186</v>
       </c>
       <c r="B11" s="3">
         <v>32</v>
@@ -1213,31 +1210,31 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B12" s="6">
+        <v>70</v>
+      </c>
+      <c r="B12" s="3">
         <v>34</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="3">
         <v>0.2</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="3">
         <v>8.1999999999999993</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="3">
         <v>0.9</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="3">
         <v>0.8</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="3">
         <v>100</v>
       </c>
       <c r="H12" s="1"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B13" s="3">
         <v>36</v>
@@ -1260,7 +1257,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B14" s="3">
         <v>39</v>
@@ -1283,7 +1280,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B15" s="3">
         <v>40</v>
@@ -1306,7 +1303,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" s="3">
         <v>41</v>
@@ -1329,7 +1326,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B17" s="3">
         <v>41</v>
@@ -1352,76 +1349,76 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="6">
+        <v>66</v>
+      </c>
+      <c r="B18" s="3">
         <v>43</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="3">
         <v>0.5</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="3">
         <v>9.6</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="3">
         <v>5.3</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="3">
         <v>1.4</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B19" s="6">
+        <v>67</v>
+      </c>
+      <c r="B19" s="3">
         <v>43</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="3">
         <v>0.3</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="3">
         <v>10.8</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="3">
         <v>1.7</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="3">
         <v>0.5</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B20" s="6">
+        <v>58</v>
+      </c>
+      <c r="B20" s="3">
         <v>47</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="3">
         <v>0.1</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="3">
         <v>11.8</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="3">
         <v>2.4</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="3">
         <v>0.9</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B21" s="3">
         <v>48</v>
@@ -1444,30 +1441,30 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B22" s="6">
+        <v>73</v>
+      </c>
+      <c r="B22" s="3">
         <v>50</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="3">
         <v>0.1</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="3">
         <v>13.1</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="3">
         <v>1.4</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="3">
         <v>0.5</v>
       </c>
-      <c r="G22" s="6">
+      <c r="G22" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B23" s="3">
         <v>52</v>
@@ -1489,77 +1486,77 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" s="5">
+      <c r="A24" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="3">
         <v>52</v>
       </c>
       <c r="C24" s="3">
         <v>0.2</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="3">
         <v>13.8</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="3">
         <v>2.4</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24" s="3">
         <v>0.3</v>
       </c>
-      <c r="G24" s="5">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B25" s="6">
+        <v>65</v>
+      </c>
+      <c r="B25" s="3">
         <v>52</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="3">
         <v>0.7</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="3">
         <v>11.9</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="3">
         <v>6.5</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F25" s="3">
         <v>1.2</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G25" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B26" s="6">
+        <v>59</v>
+      </c>
+      <c r="B26" s="3">
         <v>53</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="3">
         <v>0.3</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="3">
         <v>13.3</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E26" s="3">
         <v>1.8</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26" s="3">
         <v>0.8</v>
       </c>
-      <c r="G26" s="6">
+      <c r="G26" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B27" s="3">
         <v>57</v>
@@ -1582,99 +1579,99 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B28" s="6">
+        <v>60</v>
+      </c>
+      <c r="B28" s="3">
         <v>57</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="3">
         <v>0.1</v>
       </c>
-      <c r="D28" s="6">
+      <c r="D28" s="3">
         <v>15.2</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E28" s="3">
         <v>3.1</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28" s="3">
         <v>0.4</v>
       </c>
-      <c r="G28" s="6">
+      <c r="G28" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B29" s="6">
+        <v>74</v>
+      </c>
+      <c r="B29" s="3">
         <v>57</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="3">
         <v>0.3</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="3">
         <v>14.5</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="3">
         <v>2.4</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F29" s="3">
         <v>0.7</v>
       </c>
-      <c r="G29" s="6">
+      <c r="G29" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B30" s="5">
+      <c r="A30" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" s="3">
         <v>58</v>
       </c>
       <c r="C30" s="3">
         <v>0.4</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D30" s="3">
         <v>13.6</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30" s="3">
         <v>2.8</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30" s="3">
         <v>0.4</v>
       </c>
-      <c r="G30" s="5">
+      <c r="G30" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B31" s="6">
+        <v>63</v>
+      </c>
+      <c r="B31" s="3">
         <v>60</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="3">
         <v>0.4</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="3">
         <v>15</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E31" s="3">
         <v>1.6</v>
       </c>
-      <c r="F31" s="6">
+      <c r="F31" s="3">
         <v>0.8</v>
       </c>
-      <c r="G31" s="6">
+      <c r="G31" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B32" s="3">
         <v>61</v>
@@ -1697,30 +1694,30 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B33" s="6">
+        <v>64</v>
+      </c>
+      <c r="B33" s="3">
         <v>61</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="3">
         <v>0.5</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="3">
         <v>14.7</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E33" s="3">
         <v>3</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F33" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="G33" s="6">
+      <c r="G33" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B34" s="3">
         <v>65</v>
@@ -1743,30 +1740,30 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B35" s="6">
+        <v>61</v>
+      </c>
+      <c r="B35" s="3">
         <v>69</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="3">
         <v>0.2</v>
       </c>
-      <c r="D35" s="6">
+      <c r="D35" s="3">
         <v>18.100000000000001</v>
       </c>
-      <c r="E35" s="6">
+      <c r="E35" s="3">
         <v>0.9</v>
       </c>
-      <c r="F35" s="6">
+      <c r="F35" s="3">
         <v>0.7</v>
       </c>
-      <c r="G35" s="6">
+      <c r="G35" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B36" s="3">
         <v>77</v>
@@ -1812,30 +1809,30 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B38" s="6">
+        <v>75</v>
+      </c>
+      <c r="B38" s="3">
         <v>97</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38" s="3">
         <v>0.7</v>
       </c>
-      <c r="D38" s="6">
+      <c r="D38" s="3">
         <v>23.4</v>
       </c>
-      <c r="E38" s="6">
+      <c r="E38" s="3">
         <v>10.4</v>
       </c>
-      <c r="F38" s="6">
+      <c r="F38" s="3">
         <v>2.2000000000000002</v>
       </c>
-      <c r="G38" s="6">
+      <c r="G38" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B39" s="3">
         <v>101</v>
@@ -1858,7 +1855,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B40" s="3">
         <v>101</v>
@@ -1881,7 +1878,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B41" s="3">
         <v>102</v>
@@ -1904,7 +1901,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B42" s="3">
         <v>106</v>
@@ -1927,7 +1924,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B43" s="3">
         <v>107</v>
@@ -1950,7 +1947,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B44" s="3">
         <v>109</v>
@@ -1973,7 +1970,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B45" s="3">
         <v>125</v>
@@ -2018,31 +2015,31 @@
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A47" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B47" s="5">
+      <c r="A47" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="3">
         <v>160</v>
       </c>
       <c r="C47" s="3">
         <v>14.7</v>
       </c>
-      <c r="D47" s="5">
+      <c r="D47" s="3">
         <v>8.5</v>
       </c>
-      <c r="E47" s="5">
+      <c r="E47" s="3">
         <v>6.7</v>
       </c>
-      <c r="F47" s="5">
+      <c r="F47" s="3">
         <v>2</v>
       </c>
-      <c r="G47" s="5">
+      <c r="G47" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B48" s="3">
         <v>163</v>
@@ -2065,7 +2062,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B49" s="3">
         <v>182</v>
@@ -2088,7 +2085,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B50" s="3">
         <v>184</v>
@@ -2111,7 +2108,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B51" s="3">
         <v>207</v>
@@ -2133,31 +2130,31 @@
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A52" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B52" s="5">
+      <c r="A52" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B52" s="3">
         <v>304</v>
       </c>
       <c r="C52" s="3">
         <v>0</v>
       </c>
-      <c r="D52" s="5">
+      <c r="D52" s="3">
         <v>82.4</v>
       </c>
-      <c r="E52" s="5">
+      <c r="E52" s="3">
         <v>0.2</v>
       </c>
-      <c r="F52" s="5">
+      <c r="F52" s="3">
         <v>0.3</v>
       </c>
-      <c r="G52" s="5">
+      <c r="G52" s="3">
         <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B53" s="3">
         <v>319</v>
@@ -2180,7 +2177,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B54" s="3">
         <v>327</v>
@@ -2203,7 +2200,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B55" s="3">
         <v>329</v>
@@ -2226,7 +2223,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B56" s="3">
         <v>352</v>
@@ -2249,7 +2246,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B57" s="3">
         <v>357</v>
@@ -2272,7 +2269,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B58" s="3">
         <v>359</v>
@@ -2318,7 +2315,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B60" s="3">
         <v>380</v>
@@ -2341,7 +2338,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B61" s="3">
         <v>398</v>
@@ -2364,7 +2361,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B62" s="3">
         <v>409</v>
@@ -2387,7 +2384,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B63" s="3">
         <v>551</v>
@@ -2410,7 +2407,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B64" s="3">
         <v>579</v>
@@ -2433,7 +2430,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B65" s="3">
         <v>595</v>
@@ -2456,7 +2453,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B66" s="3">
         <v>610</v>
@@ -2479,7 +2476,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>3</v>
+        <v>187</v>
       </c>
       <c r="B67" s="3">
         <v>621</v>
@@ -2502,7 +2499,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B68" s="3">
         <v>828</v>
@@ -2554,30 +2551,30 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="G1" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B2" s="3">
         <v>15</v>
@@ -2600,7 +2597,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B3" s="3">
         <v>16</v>
@@ -2623,7 +2620,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B4" s="3">
         <v>17</v>
@@ -2646,7 +2643,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B5" s="3">
         <v>22</v>
@@ -2669,7 +2666,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B6" s="3">
         <v>23</v>
@@ -2692,7 +2689,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" s="3">
         <v>27</v>
@@ -2715,7 +2712,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B8" s="3">
         <v>30</v>
@@ -2738,7 +2735,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B9" s="3">
         <v>31</v>
@@ -2761,7 +2758,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B10" s="3">
         <v>32</v>
@@ -2784,7 +2781,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B11" s="3">
         <v>32</v>
@@ -2807,7 +2804,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B12" s="3">
         <v>34</v>
@@ -2830,7 +2827,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13" s="3">
         <v>36</v>
@@ -2853,7 +2850,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B14" s="3">
         <v>39</v>
@@ -2876,7 +2873,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B15" s="3">
         <v>40</v>
@@ -2899,7 +2896,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B16" s="3">
         <v>41</v>
@@ -2922,7 +2919,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B17" s="3">
         <v>41</v>
@@ -2945,7 +2942,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B18" s="3">
         <v>43</v>
@@ -2968,7 +2965,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B19" s="3">
         <v>43</v>
@@ -2991,7 +2988,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B20" s="3">
         <v>47</v>
@@ -3014,7 +3011,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B21" s="3">
         <v>48</v>
@@ -3037,7 +3034,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B22" s="3">
         <v>50</v>
@@ -3060,7 +3057,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B23" s="3">
         <v>52</v>
@@ -3083,7 +3080,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B24" s="3">
         <v>52</v>
@@ -3106,7 +3103,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B25" s="3">
         <v>52</v>
@@ -3129,7 +3126,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B26" s="3">
         <v>53</v>
@@ -3152,7 +3149,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B27" s="3">
         <v>57</v>
@@ -3175,7 +3172,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B28" s="3">
         <v>57</v>
@@ -3198,7 +3195,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B29" s="3">
         <v>57</v>
@@ -3221,7 +3218,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B30" s="3">
         <v>58</v>
@@ -3244,7 +3241,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B31" s="3">
         <v>60</v>
@@ -3267,7 +3264,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B32" s="3">
         <v>61</v>
@@ -3290,7 +3287,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B33" s="3">
         <v>61</v>
@@ -3313,7 +3310,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B34" s="3">
         <v>65</v>
@@ -3336,7 +3333,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B35" s="3">
         <v>69</v>
@@ -3359,7 +3356,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B36" s="3">
         <v>77</v>
@@ -3382,7 +3379,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B37" s="3">
         <v>89</v>
@@ -3405,7 +3402,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B38" s="3">
         <v>97</v>
@@ -3428,7 +3425,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B39" s="3">
         <v>101</v>
@@ -3451,7 +3448,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B40" s="3">
         <v>101</v>
@@ -3474,7 +3471,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B41" s="3">
         <v>102</v>
@@ -3497,7 +3494,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B42" s="3">
         <v>106</v>
@@ -3520,7 +3517,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B43" s="3">
         <v>107</v>
@@ -3543,7 +3540,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B44" s="3">
         <v>109</v>
@@ -3566,7 +3563,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B45" s="3">
         <v>125</v>
@@ -3589,7 +3586,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B46" s="3">
         <v>140</v>
@@ -3612,7 +3609,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B47" s="3">
         <v>160</v>
@@ -3635,7 +3632,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B48" s="3">
         <v>163</v>
@@ -3658,7 +3655,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B49" s="3">
         <v>182</v>
@@ -3681,7 +3678,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B50" s="3">
         <v>184</v>
@@ -3704,7 +3701,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B51" s="3">
         <v>207</v>
@@ -3727,7 +3724,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B52" s="3">
         <v>304</v>
@@ -3750,7 +3747,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B53" s="3">
         <v>319</v>
@@ -3773,7 +3770,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B54" s="3">
         <v>327</v>
@@ -3796,7 +3793,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B55" s="3">
         <v>329</v>
@@ -3819,7 +3816,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B56" s="3">
         <v>352</v>
@@ -3842,7 +3839,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B57" s="3">
         <v>357</v>
@@ -3865,7 +3862,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B58" s="3">
         <v>359</v>
@@ -3888,7 +3885,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B59" s="3">
         <v>372</v>
@@ -3911,7 +3908,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B60" s="3">
         <v>380</v>
@@ -3934,7 +3931,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B61" s="3">
         <v>398</v>
@@ -3957,7 +3954,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B62" s="3">
         <v>409</v>
@@ -3980,7 +3977,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B63" s="3">
         <v>551</v>
@@ -4003,7 +4000,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B64" s="3">
         <v>579</v>
@@ -4026,7 +4023,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B65" s="3">
         <v>595</v>
@@ -4049,7 +4046,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B66" s="3">
         <v>610</v>
@@ -4072,7 +4069,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B67" s="3">
         <v>621</v>
@@ -4095,7 +4092,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B68" s="3">
         <v>828</v>
@@ -4131,30 +4128,30 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="G1" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B2" s="3">
         <v>15</v>
@@ -4177,7 +4174,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B3" s="3">
         <v>16</v>
@@ -4200,7 +4197,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B4" s="3">
         <v>17</v>
@@ -4223,7 +4220,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B5" s="3">
         <v>22</v>
@@ -4246,7 +4243,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B6" s="3">
         <v>23</v>
@@ -4269,7 +4266,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B7" s="3">
         <v>27</v>
@@ -4292,7 +4289,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B8" s="3">
         <v>30</v>
@@ -4315,7 +4312,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B9" s="3">
         <v>31</v>
@@ -4338,7 +4335,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B10" s="3">
         <v>32</v>
@@ -4361,7 +4358,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B11" s="3">
         <v>32</v>
@@ -4384,7 +4381,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B12" s="3">
         <v>34</v>
@@ -4407,7 +4404,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B13" s="3">
         <v>36</v>
@@ -4430,7 +4427,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B14" s="3">
         <v>39</v>
@@ -4453,7 +4450,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B15" s="3">
         <v>40</v>
@@ -4476,7 +4473,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B16" s="3">
         <v>41</v>
@@ -4499,7 +4496,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B17" s="3">
         <v>41</v>
@@ -4522,7 +4519,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B18" s="3">
         <v>43</v>
@@ -4545,7 +4542,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B19" s="3">
         <v>43</v>
@@ -4568,7 +4565,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B20" s="3">
         <v>47</v>
@@ -4591,7 +4588,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B21" s="3">
         <v>48</v>
@@ -4614,7 +4611,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B22" s="3">
         <v>50</v>
@@ -4637,7 +4634,7 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B23" s="3">
         <v>52</v>
@@ -4660,7 +4657,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B24" s="3">
         <v>52</v>
@@ -4683,7 +4680,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B25" s="3">
         <v>52</v>
@@ -4706,7 +4703,7 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B26" s="3">
         <v>53</v>
@@ -4729,7 +4726,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B27" s="3">
         <v>57</v>
@@ -4752,7 +4749,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B28" s="3">
         <v>57</v>
@@ -4775,7 +4772,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B29" s="3">
         <v>57</v>
@@ -4798,7 +4795,7 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B30" s="3">
         <v>58</v>
@@ -4821,7 +4818,7 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B31" s="3">
         <v>60</v>
@@ -4844,7 +4841,7 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B32" s="3">
         <v>61</v>
@@ -4867,7 +4864,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B33" s="3">
         <v>61</v>
@@ -4890,7 +4887,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B34" s="3">
         <v>65</v>
@@ -4913,7 +4910,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B35" s="3">
         <v>69</v>
@@ -4936,7 +4933,7 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B36" s="3">
         <v>77</v>
@@ -4959,7 +4956,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B37" s="3">
         <v>89</v>
@@ -4982,7 +4979,7 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B38" s="3">
         <v>97</v>
@@ -5005,7 +5002,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B39" s="3">
         <v>101</v>
@@ -5028,7 +5025,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B40" s="3">
         <v>101</v>
@@ -5051,7 +5048,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B41" s="3">
         <v>102</v>
@@ -5074,7 +5071,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B42" s="3">
         <v>106</v>
@@ -5097,7 +5094,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B43" s="3">
         <v>107</v>
@@ -5120,7 +5117,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B44" s="3">
         <v>109</v>
@@ -5143,7 +5140,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B45" s="3">
         <v>125</v>
@@ -5166,7 +5163,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B46" s="3">
         <v>140</v>
@@ -5189,7 +5186,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B47" s="3">
         <v>160</v>
@@ -5212,7 +5209,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B48" s="3">
         <v>163</v>
@@ -5235,7 +5232,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B49" s="3">
         <v>182</v>
@@ -5258,7 +5255,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B50" s="3">
         <v>184</v>
@@ -5281,7 +5278,7 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B51" s="3">
         <v>207</v>
@@ -5304,7 +5301,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B52" s="3">
         <v>304</v>
@@ -5327,7 +5324,7 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B53" s="3">
         <v>319</v>
@@ -5350,7 +5347,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B54" s="3">
         <v>327</v>
@@ -5373,7 +5370,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B55" s="3">
         <v>329</v>
@@ -5396,7 +5393,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B56" s="3">
         <v>352</v>
@@ -5419,7 +5416,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B57" s="3">
         <v>357</v>
@@ -5442,7 +5439,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B58" s="3">
         <v>359</v>
@@ -5465,7 +5462,7 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B59" s="3">
         <v>372</v>
@@ -5488,7 +5485,7 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B60" s="3">
         <v>380</v>
@@ -5511,7 +5508,7 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B61" s="3">
         <v>398</v>
@@ -5534,7 +5531,7 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B62" s="3">
         <v>409</v>
@@ -5557,7 +5554,7 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B63" s="3">
         <v>551</v>
@@ -5580,7 +5577,7 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B64" s="3">
         <v>579</v>
@@ -5603,7 +5600,7 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B65" s="3">
         <v>595</v>
@@ -5626,7 +5623,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B66" s="3">
         <v>610</v>
@@ -5649,7 +5646,7 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B67" s="3">
         <v>621</v>
@@ -5672,7 +5669,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B68" s="3">
         <v>828</v>
